--- a/Document/Design/属性计算.xlsx
+++ b/Document/Design/属性计算.xlsx
@@ -760,7 +760,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -768,9 +768,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1102,13 +1099,13 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1145,7 +1142,6 @@
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1194,7 +1190,6 @@
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1258,7 +1253,6 @@
       <c r="B9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
         <v>34</v>
       </c>
